--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physics" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,14 +13,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Physics'!$A$1:$G$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Economics'!$A$1:$G$29</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +29,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,8 +51,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,7 +78,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -434,18 +442,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -482,7 +489,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Hydrogel reference thickness (H0)</t>
@@ -509,11 +516,11 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>table_s3.H0_M; range: parameter_sweep.py / lcow_economic_params.csv (hydrogel_thickness_min/max_m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Wilson et al. (2025) Sec. 2.2 (main text optimization result, H0 = 4 mm), not Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Vapor gap (L_g)</t>
@@ -540,11 +547,11 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>table_s3.L_G_M; range: parameter_sweep.py / design_space.py DesignBounds; lower bound = table_s3.VAPOR_GAP_TRANSPORT_MIN_M</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Wilson et al. (2025) Sec. 2.2 (main text optimization result, 40 mm), not Table S3; lower bound: Wilson et al. (2025) Sec. 2.2 (vapor-gap transport floor, 7 mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Insulation gap (L_ins)</t>
@@ -571,11 +578,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>table_s3.L_INS_M; range: parameter_sweep.py / design_space.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Condenser fin area ratio (A_r)</t>
@@ -602,11 +609,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>table_s3.FIN_AREA_RATIO; range: parameter_sweep.py / grid_param_sweep.py / design_space.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Tilt angle (theta)</t>
@@ -633,11 +640,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>table_s3.TILT_DEG (baseline 30 deg; Sherlock grid-sweep baseline 35 deg); range: parameter_sweep.py / design_space.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>Wilson et al. (2025) Table S3 (baseline 30 deg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Salt:polymer ratio (S/L)</t>
@@ -664,11 +671,11 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>table_s3 default / DeviceConfig; range: parameter_sweep.py / design_space.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>Wilson et al. (2025) Table S3 / Methods (4 g salt : 1 g polymer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Absorber emissivity (eps_abs)</t>
@@ -695,11 +702,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>table_s3.EPS_ABS; range: sherlock_param_sweep.tex / grid_param_sweep.py --eps-abs (3 discrete levels)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Glass transmittance (tau_glass)</t>
@@ -726,11 +733,11 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>table_s3.TAU_GLASS; range: sherlock_param_sweep.tex / grid_param_sweep.py --tau-glass (3 discrete levels)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Desorption enthalpy, LiCl (h_des)</t>
@@ -757,11 +764,11 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>table_s3.H_DES_J_PER_KG (Table S3 COMSOL value); range: parameter_sweep.py; cf. literature ~2.85e6 J/kg in salt_heat_of_desorption.csv (Diaz-Marin)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>Wilson et al. (2025) Table S3 (COMSOL value, 2.32e6 J/kg); cf. Diaz-Marin et al. (2024) ~2.85e6 J/kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Salt weight factor (DVS-cap MW scaling)</t>
@@ -788,11 +795,11 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>parameter_sweep.py::make_sweep_params (i.e. effective LiCl formula weight 35-50 g/mol)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>No literature source identified (model calibration factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ambient convection coefficient (h_amb)</t>
@@ -819,11 +826,11 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>weather/profiles.py::FIXED_H_AMB_W_M2_K (baseline profile); range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>Wilson et al. (2025) Methods (h_amb = 10 +/- 2.5 W/m^2/K, Cambridge test =&gt; upper bound 12.5); lower bound (1) is Wilson et al. (2025) Atacama Desert fitted nighttime value, not part of the +/-2.5 range</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Uptake RH / ambient RH (RH_amb)</t>
@@ -850,11 +857,11 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>parameter_sweep.py (humidity_high; baseline-mode profile only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>Wilson et al. (2025) Table S3 / main text (baseline ambient RH = 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Solar irradiance (Q_solar)</t>
@@ -881,11 +888,11 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>parameter_sweep.py (solar_irradiance_w_per_m2; baseline-mode profile only -- real-weather mode uses fetched irradiance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>Wilson et al. (2025) Methods / Sec. 2.2 (baseline solar flux = 600 W/m^2, Cambridge summertime average)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Ambient temperature (T_amb)</t>
@@ -912,11 +919,11 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>parameter_sweep.py (temperature_c; baseline-mode profile only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t>Wilson et al. (2025) Methods (assumed constant ambient temperature, 25 degC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Absorber IR emissivity (eps_abs_ir)</t>
@@ -935,15 +942,15 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>device_config.py::DeviceConfig.thermal_params() default (Case 2, 'selective surface'); categorical alternates: case1=1.0 (Wilson blackbody, exact), case3=0.0 (idealized limits); registry: sawh_bayesopt.design_space.CASE_EPS_IR -- TBD literature basis for case2/case3 numeric pairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>Case 1 (blackbody, eps=1.0): Wilson et al. (2025) (exact); Case 2/3 numeric values: no literature source identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Glass IR emissivity (eps_glass_ir)</t>
@@ -962,15 +969,15 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>device_config.py::DeviceConfig.thermal_params() default (Case 2, 'selective surface'); categorical alternates: case1=1.0 (Wilson blackbody, exact), case3=0.0 (idealized limits); registry: sawh_bayesopt.design_space.CASE_EPS_IR -- TBD literature basis for case2/case3 numeric pairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>Case 1 (blackbody, eps=1.0): Wilson et al. (2025) (exact); Case 2/3 numeric values: no literature source identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Sky temperature depression (delta T_sky)</t>
@@ -989,15 +996,15 @@
           <t>K</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>DeviceThermalParams.sky_temp_depression_c (default: no depression); non-zero only for COMSOL Atacama field-curve calibration -- TBD general range</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>No literature source identified (default: no depression assumed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Chamber convection coefficient, absorption (g_chamber)</t>
@@ -1009,22 +1016,22 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>table_s3.G_CHAMBER_M_S; duplicated in economics CSV as mass_transfer_convection_coefficient_m_s -- TBD calibration source</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>Email with Carlos Diaz-Marin; Wilson et al. (2025) Table S3 literal value is 0.0085, retained in solar_lumped tests as WILSON_TABLE_S3_G_CHAMBER_M_S for COMSOL-recreation baseline only</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Solution/brine density, LiCl (rho_sol)</t>
@@ -1043,15 +1050,15 @@
           <t>kg/m^3</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>table_s3.RHO_SOL_KG_M3 / salt_catalog.csv (NaCl/CaCl2/MgCl2 ~1200 kg/m^3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>Wilson et al. (2025) Table S3 (LiCl); NaCl/CaCl2/MgCl2 ~1200 kg/m^3 values have no literature source identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Condensation enthalpy (h_fg)</t>
@@ -1070,15 +1077,15 @@
           <t>J/kg</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>table_s3.H_FG_J_PER_KG -- TBD source (steam-table value assumed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>Wilson et al. (2025) Table S3, citing Bell et al. (2014) (CoolProp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Gel emissivity (eps_gel)</t>
@@ -1097,15 +1104,15 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>table_s3.EPS_GEL -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Condenser (Al) emissivity (eps_Al)</t>
@@ -1124,15 +1131,15 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>table_s3.EPS_AL -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Air thermal conductivity (k_air)</t>
@@ -1151,15 +1158,15 @@
           <t>W/m/K</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>table_s3.K_AIR_W_M_K</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Aluminum thermal conductivity (k_Al)</t>
@@ -1178,15 +1185,15 @@
           <t>W/m/K</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>table_s3.K_AL_W_M_K (Table S3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Hydrogel thermal conductivity (k_gel)</t>
@@ -1205,15 +1212,15 @@
           <t>W/m/K</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>table_s3.K_GEL_W_M_K (Table S3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Cover glass thermal conductivity (k_glass)</t>
@@ -1232,15 +1239,15 @@
           <t>W/m/K</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>table_s3.K_GLASS_W_M_K -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Silicone bonding-layer conductivity (k_silicone)</t>
@@ -1259,15 +1266,15 @@
           <t>W/m/K</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>table_s3.K_SILICONE_W_M_K -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>Wilson et al. (2025) Table S3 k_housing value (0.2 W/m/K, citing Azo 2024) reused here as a proxy for the silicone bonding layer; Wilson's table does not itself label this as silicone</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Aluminum density (rho_Al)</t>
@@ -1286,15 +1293,15 @@
           <t>kg/m^3</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>table_s3.RHO_AL_KG_M3 -- standard aluminum handbook value, TBD exact citation</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+          <t>Standard aluminum handbook value (no specific literature citation identified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Aluminum specific heat (cp_Al)</t>
@@ -1313,15 +1320,15 @@
           <t>J/kg/K</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>table_s3.CP_AL_J_KG_K -- standard aluminum handbook value, TBD exact citation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t>Standard aluminum handbook value (no specific literature citation identified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Cover-glass density (rho_glass)</t>
@@ -1340,15 +1347,15 @@
           <t>kg/m^3</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>table_s3.RHO_GLASS_KG_M3 (borosilicate) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+          <t>Standard borosilicate glass handbook value (no specific literature citation identified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Cover-glass specific heat (cp_glass)</t>
@@ -1367,15 +1374,15 @@
           <t>J/kg/K</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>table_s3.CP_GLASS_J_KG_K (borosilicate) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+          <t>Standard borosilicate glass handbook value (no specific literature citation identified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Gel specific heat (cp_gel)</t>
@@ -1394,15 +1401,15 @@
           <t>J/kg/K</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>table_s3.CP_GEL_J_KG_K (hydrated PAM-LiCl, water-dominated) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+          <t>No literature source identified (hydrated PAM-LiCl, water-dominated estimate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Water-vapor-in-air diffusivity (D_air)</t>
@@ -1421,15 +1428,15 @@
           <t>m^2/s</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>correlations.py::D_AIR_M2_S (Note S1 Sh = Nu analogy) -- TBD exact source</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+          <t>Wilson et al. (2025) Note S1 (Sh = Nu analogy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Air kinematic viscosity (nu_air)</t>
@@ -1448,15 +1455,15 @@
           <t>m^2/s</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>correlations.py -- standard air property near 25 degC, TBD citation</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
+          <t>Standard air property near 25 degC (no specific literature citation identified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Air Prandtl number (Pr_air)</t>
@@ -1475,15 +1482,15 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>correlations.py -- standard air property near 25 degC, TBD citation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
+          <t>Standard air property near 25 degC (no specific literature citation identified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Gravitational acceleration (g)</t>
@@ -1502,15 +1509,15 @@
           <t>m/s^2</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>correlations.py::GRAVITY_M_S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
+          <t>Standard physical constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Stefan-Boltzmann constant (sigma)</t>
@@ -1529,15 +1536,15 @@
           <t>W/m^2/K^4</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>CODATA</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Vapor-gap transport floor</t>
@@ -1556,15 +1563,15 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>table_s3.VAPOR_GAP_TRANSPORT_MIN_M (Wilson Sec. 2.2 thermobuoyancy/transport floor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+          <t>Wilson et al. (2025) Sec. 2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Universal gas constant (R)</t>
@@ -1583,15 +1590,15 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>salt_properties.py::GAS_CONSTANT_J_MOL_K (CODATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+          <t>CODATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Water molar mass (MW_w)</t>
@@ -1610,15 +1617,15 @@
           <t>kg/mol</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>salt_properties.py::WATER_MOLAR_MASS_KG_MOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
+          <t>Standard physical constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Gel water concentration upper bound (c_w,max)</t>
@@ -1637,15 +1644,15 @@
           <t>mol/m^3</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>salt_properties.py::C_W_MAX_MOL_M3 -- TBD physical basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>No literature source identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Gel water concentration lower bound (c_w,min)</t>
@@ -1664,15 +1671,15 @@
           <t>mol/m^3</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>salt_properties.py::C_W_MIN_MOL_M3 -- TBD physical basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+          <t>No literature source identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Fabrication equilibrium RH</t>
@@ -1691,11 +1698,11 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>salt_properties.py::FABRICATION_EQUILIBRIUM_RH (Methods: hydrogel cast at ~20% RH ambient)</t>
+          <t>Wilson et al. (2025) Methods (hydrogel cast at ~20% RH ambient)</t>
         </is>
       </c>
     </row>
@@ -1712,18 +1719,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -1760,7 +1766,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Discount rate (i)</t>
@@ -1772,7 +1778,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1780,18 +1786,18 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>https://www.federalregister.gov/documents/2026/01/27/2026-01591/change-in-discount-rate-for-water-resources-planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Device lifetime (L)</t>
@@ -1818,11 +1824,11 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py (integer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>No literature source identified (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Utilization factor (f_util)</t>
@@ -1834,7 +1840,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1849,11 +1855,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>No literature source identified (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Total investment factor (f_inv)</t>
@@ -1880,11 +1886,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>No literature source identified (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Maintenance cost fraction (f_maint)</t>
@@ -1911,11 +1917,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>No literature source identified (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Electricity price (p_elec)</t>
@@ -1927,7 +1933,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -1942,11 +1948,11 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>https://www.globalpetrolprices.com/electricity_prices/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Acrylamide price (c_acrylamide)</t>
@@ -1973,11 +1979,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (Table S1 note); range: parameter_sweep.py (+/-50% of baseline)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>Wilson et al. (2025) Table S1 (material quantities); price is a vendor estimate, not literature-sourced</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Additives price, composite basis (c_additives)</t>
@@ -2004,11 +2010,11 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (APS, MBAA, TEMED per Table S1); range: parameter_sweep.py (+/-50% of baseline)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>Wilson et al. (2025) Table S1 (APS, MBAA, TEMED quantities); price is a vendor estimate, not literature-sourced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Hydrogel lifetime (L_gel)</t>
@@ -2035,11 +2041,11 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv; range: parameter_sweep.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>No literature source identified (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Water price, NPV/payback scenario input (p_water)</t>
@@ -2066,11 +2072,11 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>parameter_sweep.py::_BASELINE_WATER_PRICE_USD_PER_M3 -- TBD market basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>No literature source identified (market assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Salt:polymer ratio (S/L)</t>
@@ -2097,11 +2103,11 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>See Physics sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>Wilson et al. (2025) Table S3 / Methods -- see Physics sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>BOM: aluminum heater</t>
@@ -2113,22 +2119,22 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>11.382</v>
+        <v>11.95</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (device_bom_aluminum_heater) -- TBD itemized cost basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>Wilson et al. (2025) Table S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>BOM: condenser</t>
@@ -2140,22 +2146,22 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28.455</v>
+        <v>29.87</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (device_bom_condenser) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>Wilson et al. (2025) Table S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>BOM: acrylic enclosure</t>
@@ -2174,15 +2180,15 @@
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (device_bom_acrylic_enclosure) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t>Wilson et al. (2025) Table S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>BOM: insulation</t>
@@ -2201,15 +2207,15 @@
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (device_bom_insulation) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>Wilson et al. (2025) Table S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>BOM: clamps</t>
@@ -2221,22 +2227,22 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3.474</v>
+        <v>3.47</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (device_bom_clamps) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>Wilson et al. (2025) Table S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>BOM: fixtures</t>
@@ -2255,15 +2261,15 @@
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (device_bom_fixtures) -- TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>Wilson et al. (2025) Table S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Total device BOM (C_device, derived)</t>
@@ -2275,22 +2281,22 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>52.261</v>
+        <v>54.24</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>USD/m^2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>derived: sum of the six BOM line items above</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>No literature source identified (derived: sum of the six BOM line items above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Salt price, LiCl (c_salt)</t>
@@ -2309,15 +2315,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>salt_catalog.csv -- TBD vendor/date basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>No literature source identified (vendor quote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Salt price, NaCl (c_salt)</t>
@@ -2336,15 +2342,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>salt_catalog.csv -- TBD vendor/date basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>No literature source identified (vendor quote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Salt price, CaCl2 (c_salt)</t>
@@ -2363,15 +2369,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>salt_catalog.csv -- TBD vendor/date basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>No literature source identified (vendor quote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Salt price, MgCl2 (c_salt)</t>
@@ -2390,15 +2396,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>salt_catalog.csv -- TBD vendor/date basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>No literature source identified (vendor quote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Fixed annual energy cost (C_energy,fixed)</t>
@@ -2417,15 +2423,15 @@
           <t>USD/yr</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (energy_cost_usd_per_year) -- no sweep documented</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+          <t>No literature source identified (model default, unused)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Extra half-cycle energy cost</t>
@@ -2444,15 +2450,15 @@
           <t>USD/day/half-cycle</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (energy_cost_usd_per_extra_half_cycle_per_day) -- no sweep documented</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>No literature source identified (model default, unused)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Desorption hours per day (t_des)</t>
@@ -2471,15 +2477,15 @@
           <t>hours</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (desorption_hours_per_day); not auto-tied to the physics day/night split (weather/profiles.py::PHASE_HOURS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>No literature source identified (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Max electric heat, optimizer bound (Q_elec,max)</t>
@@ -2498,15 +2504,15 @@
           <t>W/m^2</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (max_electric_heat_w_per_m2) -- an optimizer bound, not a swept axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t>No literature source identified (optimizer bound, not physical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Include desorption enthalpy in T_g solve (flag)</t>
@@ -2527,15 +2533,15 @@
           <t>boolean</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (include_desorption_enthalpy) -- not swept</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>No literature source (solver configuration flag)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Water density (rho_w)</t>
@@ -2554,11 +2560,11 @@
           <t>kg/m^3</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>lcow_economic_params.csv (water_density_kg_per_l x l_per_m3)</t>
+          <t>Standard physical constant (water density approx. 1000 kg/m^3)</t>
         </is>
       </c>
     </row>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -980,128 +980,128 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Sky temperature depression (delta T_sky)</t>
+          <t>Chamber convection coefficient, absorption (g_chamber)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Eqs. 3, 4 (T_sky = T_amb - delta T_sky)</t>
+          <t>Eq. 5 (absorption-phase mass-transfer coefficient g)</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>No literature source identified (default: no depression assumed)</t>
+          <t>Email with Carlos Diaz-Marin; Wilson et al. (2025) Table S3 literal value is 0.0085, retained in solar_lumped tests as WILSON_TABLE_S3_G_CHAMBER_M_S for COMSOL-recreation baseline only</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Chamber convection coefficient, absorption (g_chamber)</t>
+          <t>Condensation enthalpy (h_fg)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Eq. 5 (absorption-phase mass-transfer coefficient g)</t>
+          <t>Eq. 2 (condenser energy balance)</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.015</v>
+        <v>2256000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>J/kg</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Email with Carlos Diaz-Marin; Wilson et al. (2025) Table S3 literal value is 0.0085, retained in solar_lumped tests as WILSON_TABLE_S3_G_CHAMBER_M_S for COMSOL-recreation baseline only</t>
+          <t>Wilson et al. (2025) Table S3, citing Bell et al. (2014) (CoolProp)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Solution/brine density, LiCl (rho_sol)</t>
+          <t>Gel emissivity (eps_gel)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Eq. 6 (dH/dt)</t>
+          <t>Eq. 1 (eps_gc, gel-condenser radiative exchange)</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1250.2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>kg/m^3</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3 (LiCl); NaCl/CaCl2/MgCl2 ~1200 kg/m^3 values have no literature source identified</t>
+          <t>Wilson et al. (2025) Table S3</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Condensation enthalpy (h_fg)</t>
+          <t>Condenser (Al) emissivity (eps_Al)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Eq. 2 (condenser energy balance)</t>
+          <t>Eq. 1 (eps_gc, gel-condenser radiative exchange)</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2256000</v>
+        <v>0.05</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>J/kg</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3, citing Bell et al. (2014) (CoolProp)</t>
+          <t>Wilson et al. (2025) Table S3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Gel emissivity (eps_gel)</t>
+          <t>Air thermal conductivity (k_air)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Eq. 1 (eps_gc, gel-condenser radiative exchange)</t>
+          <t>Eq. 3 (conduction term); Eq. 6 (g via D_air/k_air)</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1</v>
+        <v>0.0286</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>W/m/K</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -1115,20 +1115,20 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Condenser (Al) emissivity (eps_Al)</t>
+          <t>Aluminum thermal conductivity (k_Al)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Eq. 1 (eps_gc, gel-condenser radiative exchange)</t>
+          <t>U_gel definition (gel-absorber series conductance)</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.05</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>W/m/K</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -1142,16 +1142,16 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Air thermal conductivity (k_air)</t>
+          <t>Hydrogel thermal conductivity (k_gel)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Eq. 3 (conduction term); Eq. 6 (g via D_air/k_air)</t>
+          <t>U_gel definition (gel-absorber series conductance)</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.6</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Aluminum thermal conductivity (k_Al)</t>
+          <t>Silicone bonding-layer conductivity (k_silicone)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>167</v>
+        <v>0.2</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -1189,523 +1189,439 @@
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3</t>
+          <t>Wilson et al. (2025) Table S3 k_housing value (0.2 W/m/K, citing Azo 2024) reused here as a proxy for the silicone bonding layer; Wilson's table does not itself label this as silicone</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Hydrogel thermal conductivity (k_gel)</t>
+          <t>Aluminum density (rho_Al)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U_gel definition (gel-absorber series conductance)</t>
+          <t>Eq. 2 ((rho c_p L)_cond thermal mass)</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.6</v>
+        <v>2700</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>W/m/K</t>
+          <t>kg/m^3</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3</t>
+          <t>Standard aluminum handbook value (no specific literature citation identified)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Cover glass thermal conductivity (k_glass)</t>
+          <t>Aluminum specific heat (cp_Al)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Glass thermal mass (transient desorption solvers only; not in quasi-steady Eqs. 3/4)</t>
+          <t>Eq. 2 ((rho c_p L)_cond thermal mass)</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1.2</v>
+        <v>900</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>W/m/K</t>
+          <t>J/kg/K</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3</t>
+          <t>Standard aluminum handbook value (no specific literature citation identified)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Silicone bonding-layer conductivity (k_silicone)</t>
+          <t>Water-vapor-in-air diffusivity (D_air)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>U_gel definition (gel-absorber series conductance)</t>
+          <t>Eq. 6 desorption g (Note S1 Eq. S5, Lewis-number-unity analogy)</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.2</v>
+        <v>2.62e-05</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>W/m/K</t>
+          <t>m^2/s</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3 k_housing value (0.2 W/m/K, citing Azo 2024) reused here as a proxy for the silicone bonding layer; Wilson's table does not itself label this as silicone</t>
+          <t>Wilson et al. (2025) Note S1 (Sh = Nu analogy)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Aluminum density (rho_Al)</t>
+          <t>Air kinematic viscosity (nu_air)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Eq. 2 ((rho c_p L)_cond thermal mass)</t>
+          <t>Rayleigh number, Hollands correlation (Eq. S3, feeds h_conv,g)</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2700</v>
+        <v>1.5e-05</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>kg/m^3</t>
+          <t>m^2/s</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Standard aluminum handbook value (no specific literature citation identified)</t>
+          <t>Standard air property near 25 degC (no specific literature citation identified)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Aluminum specific heat (cp_Al)</t>
+          <t>Air Prandtl number (Pr_air)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Eq. 2 ((rho c_p L)_cond thermal mass)</t>
+          <t>Defined alongside the Hollands correlation inputs; not used directly in Ra/Nu (Eq. S3 uses Ra via nu_air, alpha_air)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>900</v>
+        <v>0.71</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>J/kg/K</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Standard aluminum handbook value (no specific literature citation identified)</t>
+          <t>Standard air property near 25 degC (no specific literature citation identified)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Cover-glass density (rho_glass)</t>
+          <t>Gravitational acceleration (g)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Glass thermal mass (transient desorption solvers only)</t>
+          <t>Rayleigh number, Hollands correlation (Eq. S3)</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2230</v>
+        <v>9.81</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>kg/m^3</t>
+          <t>m/s^2</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Standard borosilicate glass handbook value (no specific literature citation identified)</t>
+          <t>Standard physical constant</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Cover-glass specific heat (cp_glass)</t>
+          <t>Stefan-Boltzmann constant (sigma)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Glass thermal mass (transient desorption solvers only)</t>
+          <t>All radiative-exchange terms (Eqs. 1, 3, 4)</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>830</v>
+        <v>5.670374419e-08</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>J/kg/K</t>
+          <t>W/m^2/K^4</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Standard borosilicate glass handbook value (no specific literature citation identified)</t>
+          <t>CODATA</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Gel specific heat (cp_gel)</t>
+          <t>Vapor-gap transport floor</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Gel thermal mass (Note S1 Eq. S1; transient desorption solvers only)</t>
+          <t>Mass-transfer inhibition constraint (g -&gt; 0 below this gap)</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3500</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>J/kg/K</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>No literature source identified (hydrated PAM-LiCl, water-dominated estimate)</t>
+          <t>Wilson et al. (2025) Sec. 2.2</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Water-vapor-in-air diffusivity (D_air)</t>
+          <t>Universal gas constant (R)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Eq. 6 desorption g (Note S1 Eq. S5, Lewis-number-unity analogy)</t>
+          <t>Eqs. 5, 6 (P_sat / (R T_g) term)</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2.62e-05</v>
+        <v>8.314462618</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>m^2/s</t>
+          <t>J/mol/K</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Note S1 (Sh = Nu analogy)</t>
+          <t>CODATA</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Air kinematic viscosity (nu_air)</t>
+          <t>Water molar mass (MW_w)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Rayleigh number, Hollands correlation (Eq. S3, feeds h_conv,g)</t>
+          <t>Eqs. 6 (dH/dt), desorption mass flux (m_des)</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1.5e-05</v>
+        <v>0.018015</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>m^2/s</t>
+          <t>kg/mol</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Standard air property near 25 degC (no specific literature citation identified)</t>
+          <t>Standard physical constant</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Air Prandtl number (Pr_air)</t>
+          <t>Gel water concentration upper bound (c_w,max)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Defined alongside the Hollands correlation inputs; not used directly in Ra/Nu (Eq. S3 uses Ra via nu_air, alpha_air)</t>
+          <t>Eq. 5 constraint (rate clipped at bound)</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.71</v>
+        <v>400000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>mol/m^3</t>
         </is>
       </c>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Standard air property near 25 degC (no specific literature citation identified)</t>
+          <t>No literature source identified</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Gravitational acceleration (g)</t>
+          <t>Gel water concentration lower bound (c_w,min)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Rayleigh number, Hollands correlation (Eq. S3)</t>
+          <t>Eq. 5 constraint (rate clipped at bound)</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>9.81</v>
+        <v>100</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>m/s^2</t>
+          <t>mol/m^3</t>
         </is>
       </c>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Standard physical constant</t>
+          <t>No literature source identified</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Stefan-Boltzmann constant (sigma)</t>
+          <t>Fabrication equilibrium RH</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>All radiative-exchange terms (Eqs. 1, 3, 4)</t>
+          <t>Initial condition for c_w (DVS isotherm equilibrium at fabrication)</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5.670374419e-08</v>
+        <v>0.2</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>W/m^2/K^4</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>CODATA</t>
+          <t>Wilson et al. (2025) Methods (hydrogel cast at ~20% RH ambient)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Vapor-gap transport floor</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Mass-transfer inhibition constraint (g -&gt; 0 below this gap)</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Condenser aluminum plate thickness (L_c)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Eq. 2 ((rho c_p L)_cond thermal mass); U_gel definition (gel-absorber aluminum backing)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Wilson et al. (2025) Sec. 2.2</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S3 (L_c = 5 mm); reused for the aluminum backing in the gel-absorber U_gel stack (same aluminum stock as the condenser plate)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Universal gas constant (R)</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Eqs. 5, 6 (P_sat / (R T_g) term)</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>8.314462618</v>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>J/mol/K</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>CODATA</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Silicone bonding-layer thickness (L_silicone)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>U_gel definition (gel-absorber series conductance)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S3 L_housing value (1 mm) reused here as a proxy for the silicone bonding layer; Wilson's table does not itself label this as silicone</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Water molar mass (MW_w)</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Eqs. 6 (dH/dt), desorption mass flux (m_des)</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0.018015</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>kg/mol</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Standard physical constant</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Gel water concentration upper bound (c_w,max)</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Eq. 5 constraint (rate clipped at bound)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>mol/m^3</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>No literature source identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Gel water concentration lower bound (c_w,min)</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Eq. 5 constraint (rate clipped at bound)</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>mol/m^3</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>No literature source identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Fabrication equilibrium RH</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Initial condition for c_w (DVS isotherm equilibrium at fabrication)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Wilson et al. (2025) Methods (hydrogel cast at ~20% RH ambient)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Composite (hydrogel) density at 20% RH (rho_gel)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dry-basis composite density for gravimetric-uptake &lt;-&gt; c_w conversions (fabrication-thickness dry mass)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1250.2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>kg/m^3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S3 (rho_gel = 1250.2 kg/m^3, density of composite at 20% RH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1"/>
+    <row r="43" ht="16" customHeight="1"/>
+    <row r="44" ht="32" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clara/github-repos/SAWH_TEAs/solar_lumped/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD43CCC-066B-A347-8AB0-6E1ECA252CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DCA147-DADE-104B-AF49-B11585E248C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Physics" sheetId="1" r:id="rId1"/>
@@ -1960,7 +1960,7 @@
         <v>132</v>
       </c>
       <c r="C6" s="2">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>133</v>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clara/github-repos/SAWH_TEAs/solar_lumped/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DCA147-DADE-104B-AF49-B11585E248C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B0692F-3E27-B542-B18B-7BBF1B6CFF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2235,7 +2235,7 @@
         <v>139</v>
       </c>
       <c r="C19" s="2">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>140</v>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Physics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Economics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Salts" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Physics'!$A$1:$G$44</definedName>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1555,14 +1556,681 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1"/>
-    <row r="41" ht="16" customHeight="1"/>
-    <row r="42" ht="16" customHeight="1"/>
-    <row r="43" ht="16" customHeight="1"/>
-    <row r="44" ht="32" customHeight="1"/>
-    <row r="45" ht="64" customHeight="1"/>
-    <row r="46" ht="32" customHeight="1"/>
-    <row r="47" ht="16" customHeight="1"/>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Desorption water-balance closure tolerance</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Guard on _integrate_desorption: |yield - c_w inventory drop| / inventory drop</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Numerical guard, not a physical constant. Trapezoid closure error is &lt;=0.09% on a sound integration; an implicit-solver failure on the T_gel-clamp kink misses by 67-99%, so anything in between separates the two populations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Water critical temperature (T_crit,H2O)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Saul-Wagner p_sat correlation (Conde 2004 App. A)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>647.096</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>IAPWS water critical point</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Water critical pressure (P_crit,H2O)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Saul-Wagner p_sat correlation (Conde 2004 App. A)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>22064000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>IAPWS water critical point</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brine mass-fraction bracket lower</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>brentq bracket for the equilibrate_salt_mf isotherm inversion</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Numerical bracket, not physical; spans every salt's validated mass-fraction range</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Brine mass-fraction bracket upper</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>brentq bracket for the equilibrate_salt_mf isotherm inversion</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Numerical bracket, not physical; above every salt's saturation mass fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Air reference temperature for thermal expansion</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>beta_air = 1 / T_ref (ideal gas), Rayleigh number in the Hollands correlation</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>300</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ideal-gas beta = 1/T at ~300 K. Stored as the reference temperature, not as beta itself: 1/300 needs 17 significant digits and the workbook keeps 15, so storing beta directly loses the last bit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Air density (rho_air)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>alpha_air = k_air / (rho_air * cp_air), Hollands correlation</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>kg/m^3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dry air, ~sea level, ~20 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Air specific heat (cp_air)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>alpha_air = k_air / (rho_air * cp_air), Hollands correlation</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>J/(kg*K)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dry air, ~20 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aluminum thermal conductivity (k_Al)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fin efficiency parameter m = sqrt(2h/(k_Al*t)) (B3)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>167</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>W/(m*K)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Temperature clamp lower bound</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>clamp_temperature_c, guards the thermal Newton solve and p_sat</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-40</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Numerical guard on the surface-temperature solve</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Temperature clamp upper bound</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>clamp_temperature_c, guards the thermal Newton solve and p_sat</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Water critical point (373.946 C) less a small margin -- the ceiling of the Saul-Wagner p_sat correlation, which returns NaN at and above T_crit. Was 120 C, which no correlation required (the LiCl/CaCl2 isotherms carry their own separate 150 C guards) and which the thermal Newton solve's OUTPUT was clamped to: a design hotter than the ceiling silently reported the ceiling instead of erroring, and dc_w/dt kinks ~15x then goes flat exactly there, which is what made implicit ODE solvers diverge on the desorption RHS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chamber dish diameter</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lab synthesis geometry</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Synthesis batch volume</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lab synthesis protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PAM-LiCl standard pour volume</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lab synthesis protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PAM-LiCl 2 g/g chamber pour volume</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration; thicker pour for similar H0 at 20% RH</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lab synthesis protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration salt:polymer ratio</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration reference point</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>g/g</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lab synthesis protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration hydrogel thickness</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chamber c_s calibration reference point</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lab synthesis protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Single-salt blend weight tolerance</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Below this ZSR weight a salt counts as absent (is_blend)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Numerical tolerance on the blend simplex</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Binary molality curve grid points</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tabulated (a_w, molality) per salt per temperature bucket</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>512</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Linear interp on a smooth monotone curve, ~1e-6 relative</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Binary molality curve temperature bucket</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Temperature quantization for the tabulated binary molality curve</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cache granularity for the per-salt molality inversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Water-activity window inset</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Inset from each salt's [rh_min, rh_max] when building the ZSR window</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Keeps the tabulated window strictly inside the correlation's validity range</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ZSR inverse table brine-fraction points</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>(T, f_b) -&gt; a_w host table, f_b axis resolution</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>256</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bilinear device-side lookup resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ZSR inverse table temperature grid lower</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Spans the gel's operating range</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ZSR inverse table temperature grid upper</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>100</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Spans the gel's operating range</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ZSR inverse table temperature grid points</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>41</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2.5 C spacing over 0-100 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Wilson condenser fan air speed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>B4 reference forced-convection air speed over the condenser</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Note S2 (Atacama system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dilution cap (maximum water activity)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Single upper bound on a_w: gates equilibrate_salt_mf, clamps equilibrium_c_w_at_rh, and sets the per-salt c_w ceiling via dilution_ceiling_c_w</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Reconciles three caps that used to disagree: per-salt rh_max (0.97, NaCl 0.99), an rh&gt;=0.99 short-circuit in equilibrium_c_w_at_rh, and C_W_MAX=400000 mol/m3 (a_w~0.948, the binding one). Needed because a_w -&gt; 1 means infinite dilution: c_w diverges and the a_w -&gt; f_b inversion goes ill-conditioned as da_w/df_b -&gt; 0.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1575,7 +2243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2570,8 +3238,393 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Case 2 selective coating premium</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B1 absorber coating cost anchor</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Premium the eps_abs_ir cost anchors encode for a selective surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Glazing cost per pane</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>B2 glazing stack capex</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Low-iron float glass, installed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Evacuated gap premium</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>B2 evacuated glazing capex</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>90</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sealed evacuated panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aluminum price</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>B3 condenser fin aluminum capex</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S2 basis: $29.87 / 13.55 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Condenser fan cost</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>B4 forced condenser cooling capex</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S2: 'Condenser fans, 50 qty, $34.50'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Condenser PV cost</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>B4 forced condenser cooling capex</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S2: 'Electronics, PV cells, 50 qty, $20.00'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Condenser fan lifetime</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B4 fan replacement interval in the NPV schedule</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Assumed service life for the condenser fans</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>salt</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>formula_weight_g_mol</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ions_per_formula</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price_usd_per_kg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>h_des_j_per_kg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>rho_solution_kg_m3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>default_sl</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>hydrate_h2o_per_formula</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>solubility_g_per_l</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LiCl</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42.394</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2850000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1250.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>845</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S3 basis. h_des: Díaz-Marín literature ~2800–3200 kJ/kg; Wilson Table S3 COMSOL uses 2320 kJ/kg (table_s3.H_DES_J_PER_KG) | hydrate: LiCl.H2O monohydrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>360</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>h_des: Weaker binding near deliquescence; ~2400-2600 kJ/kg typical for NaCl brines | hydrate: anhydrous, no stable hydrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CaCl2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>745</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>h_des: Highly hygroscopic; CaCl2·nH2O dehydration literature ~2600-2800 kJ/kg | hydrate: CaCl2.2H2O, stable ~45-175 C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MgCl2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>546</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>h_des: Moderate hygroscopicity; MgCl2 brine desorption ~2500-2700 kJ/kg | hydrate: MgCl2.2H2O at 60-120 C operating range; .6H2O dehydrates via .4H2O near 117 C.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Salt:polymer ratio (S/L)</t>
+          <t>Salt loading (SL)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -937,11 +937,15 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="E16" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Case 1 (blackbody, eps=1.0): Wilson et al. (2025) (exact); Case 2/3 numeric values are model assumptions</t>
+          <t>Case 1 (blackbody, eps=1.0): Wilson et al. (2025) (exact); Case 2/3 numeric values are model assumptions. Sweep bounds span commodity black paint (0.95) to a sputtered cermet selective surface (0.05).</t>
         </is>
       </c>
     </row>
@@ -1218,353 +1222,355 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Water-vapor-in-air diffusivity (D_air)</t>
+          <t>Gravitational acceleration (g)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Eq. 6 desorption g (Note S1 Eq. S5, Lewis-number-unity analogy)</t>
+          <t>Rayleigh number, Hollands correlation (Eq. S3)</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2.62e-05</v>
+        <v>9.81</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>m^2/s</t>
+          <t>m/s^2</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Note S1 (Sh = Nu analogy)</t>
+          <t>Standard physical constant</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Air kinematic viscosity (nu_air)</t>
+          <t>Stefan-Boltzmann constant (sigma)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Rayleigh number, Hollands correlation (Eq. S3, feeds h_conv,g)</t>
+          <t>All radiative-exchange terms (Eqs. 1, 3, 4)</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1.5e-05</v>
+        <v>5.670374419e-08</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>m^2/s</t>
+          <t>W/m^2/K^4</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Standard air property near 25 degC</t>
+          <t>CODATA</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Air Prandtl number (Pr_air)</t>
+          <t>Vapor-gap transport floor</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Defined alongside the Hollands correlation inputs; not used directly in Ra/Nu (Eq. S3 uses Ra via nu_air, alpha_air)</t>
+          <t>Mass-transfer inhibition constraint (g -&gt; 0 below this gap)</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.71</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Standard air property near 25 degC</t>
+          <t>Wilson et al. (2025) Sec. 2.2</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Gravitational acceleration (g)</t>
+          <t>Universal gas constant (R)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Rayleigh number, Hollands correlation (Eq. S3)</t>
+          <t>Eqs. 5, 6 (P_sat / (R T_g) term)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9.81</v>
+        <v>8.314462618</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>m/s^2</t>
+          <t>J/mol/K</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Standard physical constant</t>
+          <t>CODATA</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Stefan-Boltzmann constant (sigma)</t>
+          <t>Water molar mass (MW_w)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>All radiative-exchange terms (Eqs. 1, 3, 4)</t>
+          <t>Eqs. 6 (dH/dt), desorption mass flux (m_des)</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5.670374419e-08</v>
+        <v>0.018015</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>W/m^2/K^4</t>
+          <t>kg/mol</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CODATA</t>
+          <t>Standard physical constant</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Vapor-gap transport floor</t>
+          <t>Gel water concentration numerical backstop, upper</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Mass-transfer inhibition constraint (g -&gt; 0 below this gap)</t>
+          <t>Guards the isotherm inversions only: the f_b &lt;= 0 branch of equilibrium_c_w_at_rh, the DVS clamp, and the ODE rate clip in waste_heat. NOT the operating ceiling -- see Source.</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>7</v>
+        <v>400000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mol/m^3</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Sec. 2.2</t>
+          <t>Numerical backstop, not a physical bound. The binding ceiling is computed per salt and per blend by physics.dilution_ceiling_c_w as the equilibrium c_w at this sheet's 'Dilution cap (maximum water activity)' (0.98), because the same water activity corresponds to a different water inventory for every salt. 400000 mol/m3 corresponds to a_w ~ 0.948 for LiCl, so it used to bind before the dilution cap existed and reconciled the three disagreeing caps; it is now only the value the inversions return when f_b &lt;= 0 makes the algebra undefined.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Universal gas constant (R)</t>
+          <t>Gel water concentration numerical backstop, lower</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Eqs. 5, 6 (P_sat / (R T_g) term)</t>
+          <t>Guards the isotherm inversions only: degenerate returns in equilibrium_c_w_at_rh / equilibrium_c_w_from_dvs_at_rh, and the ODE rate clip in waste_heat. NOT the operating floor -- see Source.</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8.314462618</v>
+        <v>100</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>J/mol/K</t>
+          <t>mol/m^3</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>CODATA</t>
+          <t>Numerical backstop, not a physical bound. 100 mol/m3 is ~0.01-0.03 water molecules per salt formula unit, roughly 100x drier than any hydrate, i.e. no constraint at all. The binding desorption floor is computed per salt and per blend as n_hydrate * c_s (physics.hydrate_floor_c_w), with n_hydrate read from this workbook's Salts sheet 'hydrate_h2o_per_formula' column and blend-weighted over ZSR_SALTS; for baseline LiCl at S/L=4 that is 10444 mol/m3, ~100x this row. The alternative floor mode (SystemConfig(c_w_floor_mode='drh'), physics.drh_floor_c_w) stops at brine saturation instead, which is wetter still. This row is what those computed floors replaced, kept because the isotherm inversions still need a finite value to return on their degenerate branches.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Water molar mass (MW_w)</t>
+          <t>Fabrication equilibrium RH</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Eqs. 6 (dH/dt), desorption mass flux (m_des)</t>
+          <t>Initial condition for c_w (DVS isotherm equilibrium at fabrication)</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.018015</v>
+        <v>0.2</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>kg/mol</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Standard physical constant</t>
+          <t>Wilson et al. (2025) Methods (hydrogel cast at ~20% RH ambient)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Gel water concentration upper bound (c_w,max)</t>
+          <t>Condenser aluminum plate thickness (L_c)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Eq. 5 constraint (rate clipped at bound)</t>
+          <t>Eq. 2 (condenser thermal mass); U_gel definition (gel-absorber stack conductance)</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>400000</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>mol/m^3</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Device design assumption; distinct from Wilson et al. (2025) Table S3's L_c symbol, which denotes the insulation gap (tracked separately as this sheet's 'Insulation gap (L_ins)' row)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Gel water concentration lower bound (c_w,min)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Eq. 5 constraint (rate clipped at bound)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>mol/m^3</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Absorber-to-gel constant resistance (Rabs)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>U_gel definition (gel-absorber series conductance); PI-suggested lumping of R_aluminum + R_silicone into one rounded constant</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>m^2*K/W</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>R_aluminum (L_c/k_Al = 5mm/167 W/m/K = 3.0e-5) + R_silicone (L_silicone/k_silicone = 1mm/0.2 W/m/K = 5.0e-3) = 5.03e-3, rounded to 0.005 m^2 K/W</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Fabrication equilibrium RH</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Initial condition for c_w (DVS isotherm equilibrium at fabrication)</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Desorption water-balance closure tolerance</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Guard on _integrate_desorption: |yield - c_w inventory drop| / inventory drop</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Wilson et al. (2025) Methods (hydrogel cast at ~20% RH ambient)</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Numerical guard, not a physical constant. Trapezoid closure error is &lt;=0.09% on a sound integration; an implicit-solver failure on the T_gel-clamp kink misses by 67-99%, so anything in between separates the two populations.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Condenser aluminum plate thickness (L_c)</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Eq. 2 (condenser thermal mass); U_gel definition (gel-absorber stack conductance)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Device design assumption; distinct from Wilson et al. (2025) Table S3's L_c symbol, which denotes the insulation gap (tracked separately as this sheet's 'Insulation gap (L_ins)' row)</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Water critical temperature (T_crit,H2O)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Saul-Wagner p_sat correlation (Conde 2004 App. A)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>647.096</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>IAPWS water critical point</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Absorber-to-gel constant resistance (Rabs)</t>
+          <t>Water critical pressure (P_crit,H2O)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U_gel definition (gel-absorber series conductance); PI-suggested lumping of R_aluminum + R_silicone into one rounded constant</t>
+          <t>Saul-Wagner p_sat correlation (Conde 2004 App. A)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.005</v>
+        <v>22064000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>m^2*K/W</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R_aluminum (L_c/k_Al = 5mm/167 W/m/K = 3.0e-5) + R_silicone (L_silicone/k_silicone = 1mm/0.2 W/m/K = 5.0e-3) = 5.03e-3, rounded to 0.005 m^2 K/W</t>
+          <t>IAPWS water critical point</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Desorption water-balance closure tolerance</t>
+          <t>Brine mass-fraction bracket lower</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Guard on _integrate_desorption: |yield - c_w inventory drop| / inventory drop</t>
+          <t>brentq bracket for the equilibrate_salt_mf isotherm inversion</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1577,657 +1583,1700 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Numerical guard, not a physical constant. Trapezoid closure error is &lt;=0.09% on a sound integration; an implicit-solver failure on the T_gel-clamp kink misses by 67-99%, so anything in between separates the two populations.</t>
+          <t>Numerical bracket, not physical; spans every salt's validated mass-fraction range</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Water critical temperature (T_crit,H2O)</t>
+          <t>Brine mass-fraction bracket upper</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saul-Wagner p_sat correlation (Conde 2004 App. A)</t>
+          <t>brentq bracket for the equilibrate_salt_mf isotherm inversion</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>647.096</v>
+        <v>0.75</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IAPWS water critical point</t>
+          <t>Numerical bracket, not physical; above every salt's saturation mass fraction</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Water critical pressure (P_crit,H2O)</t>
+          <t>Air reference temperature for thermal expansion</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Saul-Wagner p_sat correlation (Conde 2004 App. A)</t>
+          <t>Boussinesq cross-check reference: beta_air = 1 / T_ref (ideal gas). The production Rayleigh number uses the full density ratio instead; test_governing_equations pins the two against each other.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>22064000</v>
+        <v>300</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IAPWS water critical point</t>
+          <t>Ideal-gas beta = 1/T at ~300 K. Stored as the reference temperature, not as beta itself: 1/300 needs 17 significant digits and the workbook keeps 15, so storing beta directly loses the last bit.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Brine mass-fraction bracket lower</t>
+          <t>Aluminum thermal conductivity (k_Al)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>brentq bracket for the equilibrate_salt_mf isotherm inversion</t>
+          <t>Fin efficiency parameter m = sqrt(2h/(k_Al*t)) (B3)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01</v>
+        <v>167</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>W/(m*K)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Numerical bracket, not physical; spans every salt's validated mass-fraction range</t>
+          <t>Wilson et al. (2025) Table S3</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brine mass-fraction bracket upper</t>
+          <t>Temperature clamp lower bound</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>brentq bracket for the equilibrate_salt_mf isotherm inversion</t>
+          <t>clamp_temperature_c, guards the thermal Newton solve and p_sat</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.75</v>
+        <v>-40</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Numerical bracket, not physical; above every salt's saturation mass fraction</t>
+          <t>Numerical guard on the surface-temperature solve</t>
         </is>
       </c>
     </row>
     <row r="45" ht="64" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Air reference temperature for thermal expansion</t>
+          <t>Temperature clamp upper bound</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>beta_air = 1 / T_ref (ideal gas), Rayleigh number in the Hollands correlation</t>
+          <t>clamp_temperature_c, guards the thermal Newton solve and p_sat</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>300</v>
+        <v>373.9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ideal-gas beta = 1/T at ~300 K. Stored as the reference temperature, not as beta itself: 1/300 needs 17 significant digits and the workbook keeps 15, so storing beta directly loses the last bit.</t>
+          <t>Water critical point (373.946 C) less a small margin -- the ceiling of the Saul-Wagner p_sat correlation, which returns NaN at and above T_crit. Was 120 C, which no correlation required (the LiCl/CaCl2 isotherms carry their own separate 150 C guards) and which the thermal Newton solve's OUTPUT was clamped to: a design hotter than the ceiling silently reported the ceiling instead of erroring, and dc_w/dt kinks ~15x then goes flat exactly there, which is what made implicit ODE solvers diverge on the desorption RHS.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Air density (rho_air)</t>
+          <t>Chamber dish diameter</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>alpha_air = k_air / (rho_air * cp_air), Hollands correlation</t>
+          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>kg/m^3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dry air, ~sea level, ~20 C</t>
+          <t>Lab synthesis geometry</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Air specific heat (cp_air)</t>
+          <t>Synthesis batch volume</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>alpha_air = k_air / (rho_air * cp_air), Hollands correlation</t>
+          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1005</v>
+        <v>50</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>J/(kg*K)</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dry air, ~20 C</t>
+          <t>Lab synthesis protocol</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aluminum thermal conductivity (k_Al)</t>
+          <t>PAM-LiCl standard pour volume</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fin efficiency parameter m = sqrt(2h/(k_Al*t)) (B3)</t>
+          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>W/(m*K)</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S3</t>
+          <t>Lab synthesis protocol</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Temperature clamp lower bound</t>
+          <t>PAM-LiCl 2 g/g chamber pour volume</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>clamp_temperature_c, guards the thermal Newton solve and p_sat</t>
+          <t>Chamber c_s calibration; thicker pour for similar H0 at 20% RH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-40</v>
+        <v>12.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Numerical guard on the surface-temperature solve</t>
+          <t>Lab synthesis protocol</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Temperature clamp upper bound</t>
+          <t>Chamber c_s calibration salt loading</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>clamp_temperature_c, guards the thermal Newton solve and p_sat</t>
+          <t>Chamber c_s calibration reference point</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>373.9</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>g/g</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Water critical point (373.946 C) less a small margin -- the ceiling of the Saul-Wagner p_sat correlation, which returns NaN at and above T_crit. Was 120 C, which no correlation required (the LiCl/CaCl2 isotherms carry their own separate 150 C guards) and which the thermal Newton solve's OUTPUT was clamped to: a design hotter than the ceiling silently reported the ceiling instead of erroring, and dc_w/dt kinks ~15x then goes flat exactly there, which is what made implicit ODE solvers diverge on the desorption RHS.</t>
+          <t>Lab synthesis protocol</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chamber dish diameter</t>
+          <t>Chamber c_s calibration hydrogel thickness</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
+          <t>Chamber c_s calibration reference point</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.06</v>
+        <v>2.34</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lab synthesis geometry</t>
+          <t>Lab synthesis protocol</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Synthesis batch volume</t>
+          <t>Single-salt blend weight tolerance</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
+          <t>Below this ZSR weight a salt counts as absent (is_blend)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>1e-09</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lab synthesis protocol</t>
+          <t>Numerical tolerance on the blend simplex</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PAM-LiCl standard pour volume</t>
+          <t>Binary molality curve grid points</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration (isothermal RH-schedule validation)</t>
+          <t>Tabulated (a_w, molality) per salt per temperature bucket</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lab synthesis protocol</t>
+          <t>Linear interp on a smooth monotone curve, ~1e-6 relative</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PAM-LiCl 2 g/g chamber pour volume</t>
+          <t>Binary molality curve temperature bucket</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration; thicker pour for similar H0 at 20% RH</t>
+          <t>Temperature quantization for the tabulated binary molality curve</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12.8</v>
+        <v>0.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lab synthesis protocol</t>
+          <t>Cache granularity for the per-salt molality inversion</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration salt:polymer ratio</t>
+          <t>Water-activity window inset</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration reference point</t>
+          <t>Inset from each salt's [rh_min, rh_max] when building the ZSR window</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>0.0001</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>g/g</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lab synthesis protocol</t>
+          <t>Keeps the tabulated window strictly inside the correlation's validity range</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration hydrogel thickness</t>
+          <t>ZSR inverse table brine-fraction points</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chamber c_s calibration reference point</t>
+          <t>(T, f_b) -&gt; a_w host table, f_b axis resolution</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.34</v>
+        <v>256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lab synthesis protocol</t>
+          <t>Bilinear device-side lookup resolution</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Single-salt blend weight tolerance</t>
+          <t>ZSR inverse table temperature grid lower</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Below this ZSR weight a salt counts as absent (is_blend)</t>
+          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1e-09</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Numerical tolerance on the blend simplex</t>
+          <t>Spans the gel's operating range</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Binary molality curve grid points</t>
+          <t>ZSR inverse table temperature grid upper</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tabulated (a_w, molality) per salt per temperature bucket</t>
+          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>512</v>
+        <v>100</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Linear interp on a smooth monotone curve, ~1e-6 relative</t>
+          <t>Spans the gel's operating range</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Binary molality curve temperature bucket</t>
+          <t>ZSR inverse table temperature grid points</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Temperature quantization for the tabulated binary molality curve</t>
+          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.5</v>
+        <v>41</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cache granularity for the per-salt molality inversion</t>
+          <t>2.5 C spacing over 0-100 C</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Water-activity window inset</t>
+          <t>Wilson condenser fan air speed</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inset from each salt's [rh_min, rh_max] when building the ZSR window</t>
+          <t>B4 reference forced-convection air speed over the condenser</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.0001</v>
+        <v>0.5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Keeps the tabulated window strictly inside the correlation's validity range</t>
+          <t>Wilson et al. (2025) Note S2 (Atacama system)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZSR inverse table brine-fraction points</t>
+          <t>Dilution cap (maximum water activity)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(T, f_b) -&gt; a_w host table, f_b axis resolution</t>
+          <t>Single upper bound on a_w: gates equilibrate_salt_mf, clamps equilibrium_c_w_at_rh, and sets the per-salt c_w ceiling via dilution_ceiling_c_w</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>256</v>
+        <v>0.98</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bilinear device-side lookup resolution</t>
+          <t>Reconciles three caps that used to disagree: per-salt rh_max (0.97, NaCl 0.99), an rh&gt;=0.99 short-circuit in equilibrium_c_w_at_rh, and C_W_MAX=400000 mol/m3 (a_w~0.948, the binding one). Needed because a_w -&gt; 1 means infinite dilution: c_w diverges and the a_w -&gt; f_b inversion goes ill-conditioned as da_w/df_b -&gt; 0.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZSR inverse table temperature grid lower</t>
+          <t>Cavity height (H_cav)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
+          <t>ISO 15099 aspect ratio A_g,i = H_cav / gap (Eq. 52), feeds Hollands Nu_2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Spans the gel's operating range</t>
+          <t>Device is modelled per m^2 of absorber, hence 1 m. Nu_1 dominates Nu_2 for A_g,i &gt;~ 7 at this device's Ra, so the exact value does not bind.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZSR inverse table temperature grid upper</t>
+          <t>Solar constant (G_sc)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
+          <t>Erbs (1982) diffuse-fraction decomposition, extraterrestrial irradiance</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>100</v>
+        <v>1367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>W/m^2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Spans the gel's operating range</t>
+          <t>Standard solar constant (Duffie &amp; Beckman)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ZSR inverse table temperature grid points</t>
+          <t>Ground albedo (POA transposition)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(T, f_b) -&gt; a_w host table, temperature axis</t>
+          <t>Liu &amp; Jordan isotropic-sky ground-reflected term</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>41</v>
+        <v>0.2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.5 C spacing over 0-100 C</t>
+          <t>Generic ground reflectance (Duffie &amp; Beckman)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wilson condenser fan air speed</t>
+          <t>Minimum cos(zenith) for DNI division</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B4 reference forced-convection air speed over the condenser</t>
+          <t>DNI = (GHI - DHI) / cos(zenith); clamp on the divisor</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Note S2 (Atacama system)</t>
+          <t>Below ~3 deg solar elevation the division blows up on near-zero cos(zenith); clamp rather than emit a spurious POA spike.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dilution cap (maximum water activity)</t>
+          <t>Baseline phase time step</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Single upper bound on a_w: gates equilibrate_salt_mf, clamps equilibrium_c_w_at_rh, and sets the per-salt c_w ceiling via dilution_ceiling_c_w</t>
+          <t>Baseline/replay weather profile sampling interval</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.98</v>
+        <v>100</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Note S1 / COMSOL time step</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Baseline half-cycle duration</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Baseline weather profile absorption and desorption phase length</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) 12 h / 12 h duty cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Solar night threshold</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GHI below this counts as night when segmenting a real-weather day</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>W/m^2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Numerical threshold on measured GHI noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Isosteric h_des finite-difference step</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Clausius-Clapeyron d(ln a_w)/d(1/T) central difference</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Numerical step, not physical. Small against the isotherm's temperature scale, large enough to stay off the a_w round-off floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Instant-equilibrium g scale factor</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mass-transfer coefficient multiplier for the instant-equilibrium limit</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Numerical, not physical. Big enough that the residual driving force is negligible against the ODE relative tolerance, small enough that g*driving stays far from float overflow at any reachable p_sat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ODE relative tolerance</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LSODA rtol for the coupled Eqs. 1-6 + Eq. 2 half-cycle integration</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Solver tolerance, not a physical constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ODE absolute tolerance</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LSODA atol for the coupled Eqs. 1-6 + Eq. 2 half-cycle integration</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Solver tolerance, not a physical constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Desorption mass-flux bracket upper</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>brentq bracket ceiling on m_des in the coupled desorption solve</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>kg/m^2/s</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Numerical bracket, not physical; ~2 orders above any reachable desorption flux</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Waste-heat: contactor thermal mass</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Contactor energy balance (dT_contactor/dt)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>J/m^2/K</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Waste-heat: contactor area</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Contactor energy balance; per-m^2 basis of the two-bed device</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Device is modelled per m^2 of contactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Waste-heat: contactor emissivity</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Contactor radiative exchange with the condenser</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Non-selective contactor surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Waste-heat: vacuum gap</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Contactor-condenser vapour path length in the evacuated chamber</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Waste-heat: chamber condensing pressure</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Evacuated-chamber operating pressure (~30 mbar)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Waste-heat: contactor UA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Series conductance from the waste-heat HX into the contactor</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>800</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>W/K</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Waste-heat: condenser plate thickness</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Condenser thermal mass ((rho c_p L)_cond)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.003175</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1/8 inch aluminium plate (0.125 in x 0.0254 m/in)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Waste-heat: temperature clamp upper bound</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>clamp_temperature_c, guards the two-bed thermal solve and the Tetens p_sat</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>120</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Kept at 120 C rather than sharing the solar package's 373.9 C: that ceiling is the Saul-Wagner correlation's critical-point limit, and waste_heat uses Tetens (Magnus), which has no such ceiling. 120 C sits well above the 58 C waste-heat source, so the clamp is a divergence guard here, not a physical bound. The lower bound is shared (this sheet's 'Temperature clamp lower bound').</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Waste-heat: reference pressure</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pressure at which nu_air, alpha_air and D_air are quoted; Knudsen scaling</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Standard atmosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Waste-heat: stream inlet temperature (T_wh,in)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Waste-heat HX inlet, drives the desorbing bed</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>58</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Low-grade industrial waste-heat stream assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Waste-heat: stream specific heat (cp_wh)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Waste-heat HX energy balance</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4180</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>J/kg/K</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Liquid water at ~58 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Waste-heat: stream mass flow (m_wh)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Waste-heat HX energy balance, per m^2 of contactor</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>kg/s/m^2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Waste-heat: HX UA (UA_hx)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Waste-heat HX conductance; series with the contactor UA</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>W/K</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Waste-heat: vacuum conductance base (C_vac)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vapour conductance from desorbing bed to condenser</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>8e-09</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>kg/s/Pa/m^2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Waste-heat: vacuum conductance lower bound</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Optimizer / sweep bound on C_vac</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1e-10</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>kg/s/Pa/m^2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Sweep bound, not physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Waste-heat: vacuum conductance upper bound</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Optimizer / sweep bound on C_vac</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>kg/s/Pa/m^2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Sweep bound, not physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Waste-heat: desorber RH switch threshold</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Half-cycle ends when the vapour-gap RH outside the desorber falls to this</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Reconciles three caps that used to disagree: per-salt rh_max (0.97, NaCl 0.99), an rh&gt;=0.99 short-circuit in equilibrium_c_w_at_rh, and C_W_MAX=400000 mol/m3 (a_w~0.948, the binding one). Needed because a_w -&gt; 1 means infinite dilution: c_w diverges and the a_w -&gt; f_b inversion goes ill-conditioned as da_w/df_b -&gt; 0.</t>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cycle control set point</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Waste-heat: maximum half-cycle duration (tau_half)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Half-cycle timeout; the RH threshold usually ends the cycle earlier</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>21600</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>6 h cap on a half-cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Waste-heat: mass-transfer resistance coefficient (k_m)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Bed mass-transfer resistance, per kg of composite per m^2</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1/(kg/m^2)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Waste-heat: pressure-drop coefficient (k_p)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bed pressure drop, per kg/s per m^2</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1/(kg/s/m^2)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat device design assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Waste-heat: ambient temperature (T_amb)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Contactor and condenser ambient losses</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>32</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat siting assumption; distinct from the solar device's 25 degC</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Waste-heat: ambient RH (RH_amb)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Absorption-phase driving humidity</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Two-bed waste-heat siting assumption; distinct from the solar device's 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Waste-heat: hydrogel depletion time constant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ramp over which a depleted bed's uptake is driven to zero</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>600</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Numerical ramp, not physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Waste-heat: weather profile time step</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Real-weather profile resampling interval</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>60</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Profile resolution for the two-bed cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Waste-heat: inventory sample time step</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Water-inventory sampling interval inside a half-cycle</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>6</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Diagnostic sampling resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Condenser forced-air speed</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>B4 forced condenser convection (h_cond)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0 = passive. Wilson et al. (2025) Note S2 runs a 0.5 m/s fan array; the 1.5 m/s upper bound allows ~3x that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Seal / open offset from sunrise-sunset</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>A1 chamber seal and open times</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hours the seal/open boundaries move off GHI sunrise/sunset. +/-4 h covers sealing before dawn through holding shut well past dusk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Instant-equilibrium residual driving-force tolerance</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Guard on _integrate_absorption under instant_equilibrium: |dc_w/dt| at the end of absorption, relative to its value at the start</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Numerical guard, not a physical constant. instant_equilibrium means the gel reaches equilibrium with the ambient RH, i.e. the residual driving force goes to zero -- the defining property, and checkable without a closed-form target for the equilibrium c_w (which cap binds, brine isotherm vs DVS uptake, varies with RH). Measured residual ratio is &lt;=1.5e-15 across RH 0.3-0.95 and the ZSR blends; a finite-g run sits at 1.1e-1, so this threshold has ~9 orders of headroom above a sound instant-equilibrium run and ~5 orders below a finite-g one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Atmospheric pressure (P0)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sea-level reference: Tsilingiris Eq. 5 x_v, Marrero-Mason D_air pressure scaling, and the h_amb density reference. Per-site pressure comes from SystemConfig.site_elevation_m.</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Standard atmosphere (sea level); lower it for high-altitude sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Water-vapor-in-air diffusivity (D_air)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Waste-heat vacuum-gap g (Note S1 Eq. S5). solar_lumped now uses physics.d_h2o_air_m2_s (Marrero &amp; Mason 1972) at the gap film temperature instead.</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2.62e-05</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>m^2/s</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Note S1 (Sh = Nu analogy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Air kinematic viscosity (nu_air)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Waste-heat vacuum-gap Rayleigh number. solar_lumped now uses physics.humid_air_props (Tsilingiris 2008) at the gap film temperature instead.</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>m^2/s</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Standard air property near 25 degC</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Air density (rho_air)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Waste-heat alpha_air = k_air/(rho_air*cp_air). solar_lumped now uses physics.humid_air_props instead.</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>kg/m^3</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Dry air, ~sea level, ~20 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Air specific heat (cp_air)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Waste-heat alpha_air = k_air/(rho_air*cp_air). solar_lumped now uses physics.humid_air_props instead.</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>J/(kg*K)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Dry air, ~20 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ambient convection density exponent</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>h_amb scales as (rho_amb/rho_ref)^n; n=0.5 laminar flat plate, 0.8 turbulent</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Nu ~ Re^n Pr^(1/3), Re = uL/nu with nu ~ 1/rho; device Re ~ 3e4 is laminar (transition 5e5)</t>
         </is>
       </c>
     </row>
@@ -2243,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2605,7 +3654,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Salt:polymer ratio (S/L)</t>
+          <t>Salt loading (SL)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2798,300 +3847,292 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Salt price, LiCl (c_salt)</t>
+          <t>Desorption hours per day (t_des)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
+          <t>Annualized device cost (C_elec term)</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.alibaba.com/product-detail/99-Inorganic-Chemicals-Lithium-Chloride-Accelerator_1601710554952.html?spm=a2700.prosearch.normal_offer.d_title.40c667afgDIVvc&amp;priceId=828a9f958c9b48239f1fd7ba0fe194ed</t>
+          <t>Model assumption</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Salt price, NaCl (c_salt)</t>
+          <t>Max electric heat, optimizer bound (Q_elec,max)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
+          <t>Optimizer bound only -- baseline passive device has Q_elec=0</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.045</v>
+        <v>1500</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>W/m^2</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Vendor quote</t>
+          <t>Optimizer bound, not physical</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Salt price, CaCl2 (c_salt)</t>
+          <t>Include desorption enthalpy in T_g solve (flag)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0.17</v>
+          <t>Eq. 1 (gel heat balance solve mode)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Vendor quote</t>
+          <t>Solver configuration flag</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Salt price, MgCl2 (c_salt)</t>
+          <t>Water density (rho_w)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
+          <t>LCOW denominator; NPV revenue</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.01985</v>
+        <v>1000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg/m^3</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Vendor quote</t>
+          <t>Standard physical constant (water density approx. 1000 kg/m^3)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Desorption hours per day (t_des)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Annualized device cost (C_elec term)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Model assumption</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>N,N'-methylenebisacrylamide price, MBA (c_MBA)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sorbent (hydrogel) replacement cost</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/product-detail/Hight-Quatity-N-N-Methylenebisacrylamide-CAS_60764000386.html?spm=a2700.prosearch.normal_offer.d_title.55c567afiK7wkp&amp;priceId=b229c05ca34742d68704f1593eac8739</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Max electric heat, optimizer bound (Q_elec,max)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Optimizer bound only -- baseline passive device has Q_elec=0</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>W/m^2</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Optimizer bound, not physical</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tetramethylethylenediamine price, TEMED (c_TEMED)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sorbent (hydrogel) replacement cost</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/product-detail/Tetramethylethylenediamine-110-18-9_1601622983671.html?spm=a2700.prosearch.normal_offer.d_title.169b67afgD440s&amp;priceId=22949719cda64b4a9898fc6baeb36e1a</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Include desorption enthalpy in T_g solve (flag)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Eq. 1 (gel heat balance solve mode)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Solver configuration flag</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>De-ionized water price, hydrogel manufacturing (c_water_gel)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sorbent (hydrogel) replacement cost</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://uswatersystems.com/products/us-water-patriot-triplex-2-0-gpm-high-capacity-di-pod-system-320-di-pod-s</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Water density (rho_w)</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>LCOW denominator; NPV revenue</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>kg/m^3</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Standard physical constant (water density approx. 1000 kg/m^3)</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LiCl mass fraction, salt (Table S1 recipe)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Table S1 recipe completeness only -- the sorbent cost prices salt via salt loading x the Salts sheet price, not this fraction. Kept so the six Table S1 mass fractions sum to 1 and the polymer sub-mix renormalization below is checkable.</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.2489420394119936</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>kg component / kg hydrogel batch</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Wilson et al. (2025) Table S1</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>N,N'-methylenebisacrylamide price, MBA (c_MBA)</t>
+          <t>Acrylamide mass fraction, AM (Table S1 recipe)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
+          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.48</v>
+        <v>0.06415972727807956</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg component / kg hydrogel batch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.alibaba.com/product-detail/Hight-Quatity-N-N-Methylenebisacrylamide-CAS_60764000386.html?spm=a2700.prosearch.normal_offer.d_title.55c567afiK7wkp&amp;priceId=b229c05ca34742d68704f1593eac8739</t>
+          <t>Wilson et al. (2025) Table S1</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tetramethylethylenediamine price, TEMED (c_TEMED)</t>
+          <t>Ammonium persulfate mass fraction, APS (Table S1 recipe)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
+          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>0.0002182694392629385</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg component / kg hydrogel batch</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.alibaba.com/product-detail/Tetramethylethylenediamine-110-18-9_1601622983671.html?spm=a2700.prosearch.normal_offer.d_title.169b67afgD440s&amp;priceId=22949719cda64b4a9898fc6baeb36e1a</t>
+          <t>Wilson et al. (2025) Table S1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>De-ionized water price, hydrogel manufacturing (c_water_gel)</t>
+          <t>N,N'-methylenebisacrylamide mass fraction, MBA (Table S1 recipe)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost</t>
+          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.000383407501863188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg component / kg hydrogel batch</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://uswatersystems.com/products/us-water-patriot-triplex-2-0-gpm-high-capacity-di-pod-system-320-di-pod-s</t>
+          <t>Wilson et al. (2025) Table S1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LiCl mass fraction, salt (Table S1 recipe)</t>
+          <t>Tetramethylethylenediamine mass fraction, TEMED (Table S1 recipe)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3100,7 +4141,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.2489420394119936</v>
+        <v>0.000183805843589843</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3116,7 +4157,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Acrylamide mass fraction, AM (Table S1 recipe)</t>
+          <t>De-ionized water mass fraction (Table S1 recipe)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3125,7 +4166,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.06415972727807956</v>
+        <v>0.6861127505252107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3141,116 +4182,116 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ammonium persulfate mass fraction, APS (Table S1 recipe)</t>
+          <t>Case 2 selective coating premium</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
+          <t>B1 absorber coating cost anchor</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002182694392629385</v>
+        <v>10</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kg component / kg hydrogel batch</t>
+          <t>USD/m^2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S1</t>
+          <t>Premium the eps_abs_ir cost anchors encode for a selective surface</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>N,N'-methylenebisacrylamide mass fraction, MBA (Table S1 recipe)</t>
+          <t>Glazing cost per pane</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
+          <t>B2 glazing stack capex</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.000383407501863188</v>
+        <v>12</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>kg component / kg hydrogel batch</t>
+          <t>USD/m^2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S1</t>
+          <t>Low-iron float glass, installed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tetramethylethylenediamine mass fraction, TEMED (Table S1 recipe)</t>
+          <t>Evacuated gap premium</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
+          <t>B2 evacuated glazing capex</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.000183805843589843</v>
+        <v>90</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kg component / kg hydrogel batch</t>
+          <t>USD/m^2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S1</t>
+          <t>Sealed evacuated panel</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>De-ionized water mass fraction (Table S1 recipe)</t>
+          <t>Aluminum price</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sorbent (hydrogel) replacement cost -- Table S1 mass-fraction basis</t>
+          <t>B3 condenser fin aluminum capex</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.6861127505252107</v>
+        <v>2.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kg component / kg hydrogel batch</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S1</t>
+          <t>Wilson et al. (2025) Table S2 basis: $29.87 / 13.55 kg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Case 2 selective coating premium</t>
+          <t>Condenser fan cost</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B1 absorber coating cost anchor</t>
+          <t>B4 forced condenser cooling capex</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>34.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3259,23 +4300,23 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Premium the eps_abs_ir cost anchors encode for a selective surface</t>
+          <t>Wilson et al. (2025) Table S2: 'Condenser fans, 50 qty, $34.50'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Glazing cost per pane</t>
+          <t>Condenser PV cost</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B2 glazing stack capex</t>
+          <t>B4 forced condenser cooling capex</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3284,73 +4325,73 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Low-iron float glass, installed</t>
+          <t>Wilson et al. (2025) Table S2: 'Electronics, PV cells, 50 qty, $20.00'</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Evacuated gap premium</t>
+          <t>Condenser fan lifetime</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B2 evacuated glazing capex</t>
+          <t>B4 fan replacement interval in the NPV schedule</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>USD/m^2</t>
+          <t>years</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sealed evacuated panel</t>
+          <t>Assumed service life for the condenser fans</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aluminum price</t>
+          <t>Waste-heat BOM: vacuum pump</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B3 condenser fin aluminum capex</t>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.2</v>
+        <v>3500</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>USD/m^2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S2 basis: $29.87 / 13.55 kg</t>
+          <t>Patent Fig. 1 item (28)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Condenser fan cost</t>
+          <t>Waste-heat BOM: chambers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B4 forced condenser cooling capex</t>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>34.5</v>
+        <v>1050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3359,23 +4400,23 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S2: 'Condenser fans, 50 qty, $34.50'</t>
+          <t>Patent Fig. 1 items (22A, 22B) with door assemblies (38)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Condenser PV cost</t>
+          <t>Waste-heat BOM: valves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B4 forced condenser cooling capex</t>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3384,32 +4425,532 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Wilson et al. (2025) Table S2: 'Electronics, PV cells, 50 qty, $20.00'</t>
+          <t>Patent Fig. 1 three-way valve (32) + check valve (30)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Condenser fan lifetime</t>
+          <t>Waste-heat BOM: condenser</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B4 fan replacement interval in the NPV schedule</t>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>850</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>USD/m^2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Assumed service life for the condenser fans</t>
+          <t>Patent Fig. 1 item (24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Waste-heat BOM: coolant source</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>325</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Patent Fig. 1 item (26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Waste-heat BOM: water pump</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>165</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Patent Fig. 1 item (34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Waste-heat BOM: controller and sensors</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>800</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Patent Fig. 1 controller (16) + sensors (36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Waste-heat BOM: purge pump</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>400</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Patent Fig. 1 item (234)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Waste-heat BOM: structural</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Annualized device cost (C_device = sum of BOM line items)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>USD/m^2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Structural housing, manifolds, plumbing, fasteners</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Waste-heat: fixed annual energy cost</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Annualized device cost (fixed energy term)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>USD/m^2/yr</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Zero by default; parasitic loads are priced per half-cycle instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Waste-heat: energy cost per extra half-cycle per day</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Annualized device cost (per-cycle energy term)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>USD/m^2/yr</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Zero by default; set to price vacuum-pump work above 1 half-cycle/day</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hydrogel additives cost per kg composite (APS + MBA + TEMED)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sorbent (hydrogel) replacement cost -- simplified waste-heat TEA</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0072148</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>USD/kg composite</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Table S1 APS/MBA/TEMED lumped per kg of composite. The solar package instead prices the four polymer components individually off this sheet's Table S1 mass-fraction rows; this lump is the waste-heat TEA's coarser equivalent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: vacuum pump shaft power</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>45</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>W/m^2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Roughing pump (28) during desorption half-cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: vacuum pump motor efficiency</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Roughing pump (28) motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: vacuum pump operating hours</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (annual kWh = grid power * hours * 365)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>12</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>hours/day</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Matches the desorption window</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: water pump shaft power</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>W/m^2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Product-water transfer pump (34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: water pump motor efficiency</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Product-water transfer pump (34) motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: water pump operating hours</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (annual kWh = grid power * hours * 365)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>hours/day</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Product-water transfer duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: purge pump shaft power</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>W/m^2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Manifold / valve purge pump (234)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: purge pump motor efficiency</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Manifold / valve purge pump (234) motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: purge pump operating hours</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (annual kWh = grid power * hours * 365)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>hours/day</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Manifold / valve purge duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: controller and sensors shaft power</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>W/m^2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Controller (16) + sensors (36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: controller and sensors efficiency</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (grid power = shaft power / motor efficiency)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Controls and instrumentation power supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Waste-heat parasitic: controller and sensors operating hours</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Parasitic electricity (annual kWh = grid power * hours * 365)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>24</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>hours/day</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Always on</t>
         </is>
       </c>
     </row>
@@ -3425,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3624,6 +5165,42 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LiBr</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>86.845</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1427</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Isotherm: Patek &amp; Klomfar (2006) Int J Refrig 29(4) 566-578 Eq.(1)+Table 4, transcribed in physics._PATEK_LIBR from patek2006.tex and validated against that paper's Table 9 to 0.15% (the Saul-Wagner vs IAPWS-95 gap). Duhring form, valid 273-483 K and 0-75 wt%; fitted to 1449 points incl. Lenard 1992 (398-483 K) and Feuerecker 1993 (318-462 K), so 155 C is measured, not extrapolated. NOTE Patek collected and REJECTED Patil &amp; Tripathi 1990 (0 of 40 points, RMS 4.76%), which is half of the local libr_*.csv data; those CSVs are now validation only and reproduce his 4.76% verdict (see data/materials/fit_libr_saturation.py). h_des: isosteric Clausius-Clapeyron on that isotherm (2670-2790 kJ/kg near saturation over 10-210 C); tabulated 2550 kJ/kg is only the h_des_mode='constant' fallback. Saturation: temperature-resolved via physics._CRYSTALLIZATION_LINE['LiBr'], derived by inverting the isotherm at Greenspan (1977) NBS 81A deliquescence humidities (0-100 C, matches to 0.005 in a_w); solubility_g_per_l is INERT for LiBr, kept only as the 25 C reference. hydrate: LiBr.H2O assumed and UNVERIFIED -- the single crystallization branch does not resolve LiBr's hydrate transitions; check before relying on hydrate_floor_c_w. price_usd_per_kg 2.00 set by user directive (2026-08-15), not a sourced quote.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Numerical, not physical. Big enough that the residual driving force is negligible against the ODE relative tolerance, small enough that g*driving stays far from float overflow at any reachable p_sat.</t>
+          <t>Numerical, not physical. Big enough that the residual driving force is negligible against the ODE relative tolerance, small enough that g*driving stays far from float overflow at any reachable p_sat -- and small enough to afford: the g -&gt; inf limit is stiff, so the JAX explicit solver's step count scales with this factor. Lowered 1e6 -&gt; 1e5 after a convergence study (gpu_sweep/probe_instant_g_scale.py) measured annual yield 0.12% from the 1e6 answer at ~2.6x less cost; 1e4 drifts 0.79%, which is why it is not 1e4. The residual-driving-force guard sits ~8 orders above the resulting ratio.</t>
         </is>
       </c>
     </row>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Numerical, not physical. Big enough that the residual driving force is negligible against the ODE relative tolerance, small enough that g*driving stays far from float overflow at any reachable p_sat -- and small enough to afford: the g -&gt; inf limit is stiff, so the JAX explicit solver's step count scales with this factor. Lowered 1e6 -&gt; 1e5 after a convergence study (gpu_sweep/probe_instant_g_scale.py) measured annual yield 0.12% from the 1e6 answer at ~2.6x less cost; 1e4 drifts 0.79%, which is why it is not 1e4. The residual-driving-force guard sits ~8 orders above the resulting ratio.</t>
+          <t>Numerical, not physical, and no longer on any production path: instant equilibrium is now imposed as the equilibrium constraint itself (physics.equilibrium_t_gel_desorption_c / equilibrium_c_w_absorption), not by scaling g until Eq. 5's residual is negligible. This factor survives only as the legacy penalty route's setting, which tests/test_local_equilibrium.py pins the constraint against; 1e6 is the most converged reference of the values measured (1e5 sits 0.12% from it, 1e4 0.79%). It was briefly lowered to 1e5 to buy sweep time back when the penalty was still in use -- the constraint made that trade unnecessary, so it is restored.</t>
         </is>
       </c>
     </row>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Salt weight factor (DVS-cap MW scaling)</t>
+          <t>Salt weight factor (dry-mass MW scaling)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Model calibration factor</t>
+          <t>Scales MW_salt when converting composite state to dry mass / gravimetric uptake. Was named for the DVS uptake cap it also fed; that cap is gone (water uptake now comes from the salt-in-water activity model alone), but the dry-mass bookkeeping it scales remains. Value unchanged.</t>
         </is>
       </c>
     </row>
@@ -3277,6 +3277,26 @@
       <c r="G107" t="inlineStr">
         <is>
           <t>Nu ~ Re^n Pr^(1/3), Re = uL/nu with nu ~ 1/rho; device Re ~ 3e4 is laminar (transition 5e5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Dry composite density (rho_dry)</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>553.4659316075422</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>kg/m3</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Dry-basis density of the PAM-LiCl composite: rho_composite(20% RH) 1250.2 / (1 + 1.2589), where 1.2589 g/g is the measured composite moisture content at the 20% RH fabrication equilibrium (Wilson Note S2 DVS). Recorded as a scalar because the DVS *isotherm* is no longer used as a sorption model -- water uptake now comes from the salt-in-water activity model alone (physics.water_activity_from_c_w). This is a mass/density calibration, not a sorption curve: it converts between dry composite mass and footprint volume for costing and gravimetric reporting. Value is bit-identical to what the derived expression returned.</t>
         </is>
       </c>
     </row>

--- a/solar_lumped/docs/parameters.xlsx
+++ b/solar_lumped/docs/parameters.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Physics" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="Salts" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Physics'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Physics'!$A$1:$H$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Economics'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -436,15 +436,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16.1640625" customWidth="1" min="5" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16.1640625" customWidth="1" min="5" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -480,6 +480,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -509,7 +514,8 @@
       <c r="F2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Sec. 2.2 (main text optimization result, H0 = 4 mm)</t>
         </is>
@@ -523,7 +529,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hollands h_conv,g correlation (feeds Eqs. 1, 5, 6)</t>
+          <t>h_conv,g = Nu k_air/(L_g - H): ISO 15099 5.3.3.5 downward-facing Nu at every converged state (Hollands only on the solver's inverted T_cond &gt; T_gel branch). Feeds Eqs. 1, 2, 5, 6.</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -540,7 +546,8 @@
       <c r="F3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Sec. 2.2 (main text optimization result, 40 mm); lower bound: Wilson et al. (2025) Sec. 2.2 (vapor-gap transport floor, 7 mm)</t>
         </is>
@@ -571,7 +578,8 @@
       <c r="F4" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -602,7 +610,8 @@
       <c r="F5" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -616,7 +625,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Hollands Nu correlation (Eq. S3; feeds Eqs. 1, 2, 5, 6 via h_conv,g)</t>
+          <t>Gap Nu correlations (ISO 15099 5.3.3.5 stratified; Hollands Eq. S3 on the inverted branch); feeds Eqs. 1, 2, 5, 6 via h_conv,g. Also the POA transposition when --poa.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -633,7 +642,8 @@
       <c r="F6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3 (baseline 30 deg)</t>
         </is>
@@ -664,7 +674,8 @@
       <c r="F7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3 / Methods (4 g salt : 1 g polymer)</t>
         </is>
@@ -695,7 +706,8 @@
       <c r="F8" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -726,7 +738,8 @@
       <c r="F9" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -757,7 +770,8 @@
       <c r="F10" s="2" t="n">
         <v>3200000</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3 (COMSOL value, 2.32e6 J/kg); cf. Diaz-Marin et al. (2024) ~2.85e6 J/kg</t>
         </is>
@@ -788,7 +802,8 @@
       <c r="F11" s="2" t="n">
         <v>1.18</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Scales MW_salt when converting composite state to dry mass / gravimetric uptake. Was named for the DVS uptake cap it also fed; that cap is gone (water uptake now comes from the salt-in-water activity model alone), but the dry-mass bookkeeping it scales remains. Value unchanged.</t>
         </is>
@@ -819,7 +834,8 @@
       <c r="F12" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Methods (h_amb = 10 +/- 2.5 W/m^2/K, Cambridge test =&gt; upper bound 12.5); lower bound (1) is Wilson et al. (2025) Atacama Desert fitted nighttime value, not part of the +/-2.5 range</t>
         </is>
@@ -850,7 +866,8 @@
       <c r="F13" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3 / main text (baseline ambient RH = 0.5)</t>
         </is>
@@ -881,7 +898,8 @@
       <c r="F14" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Methods / Sec. 2.2 (baseline solar flux = 600 W/m^2, Cambridge summertime average)</t>
         </is>
@@ -912,7 +930,8 @@
       <c r="F15" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Methods (assumed constant ambient temperature, 25 degC)</t>
         </is>
@@ -943,7 +962,8 @@
       <c r="F16" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Case 1 (blackbody, eps=1.0): Wilson et al. (2025) (exact); Case 2/3 numeric values are model assumptions. Sweep bounds span commodity black paint (0.95) to a sputtered cermet selective surface (0.05).</t>
         </is>
@@ -970,7 +990,8 @@
       </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Case 1 (blackbody, eps=1.0): Wilson et al. (2025) (exact); Case 2/3 numeric values are model assumptions</t>
         </is>
@@ -997,7 +1018,8 @@
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Email with Carlos; Wilson et al. (2025) Table S3 literal value is 0.0085, retained in solar_lumped tests as WILSON_TABLE_S3_G_CHAMBER_M_S for COMSOL-recreation baseline only</t>
         </is>
@@ -1024,7 +1046,8 @@
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3 (rho_gel = 1250.2 kg/m^3, density of composite at 20% RH, LiCl); NaCl/CaCl2/MgCl2 values assumed ~1200 kg/m^3</t>
         </is>
@@ -1051,7 +1074,8 @@
       </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3, citing Bell et al. (2014) (CoolProp)</t>
         </is>
@@ -1078,7 +1102,8 @@
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -1105,7 +1130,8 @@
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -1132,7 +1158,8 @@
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -1159,7 +1186,8 @@
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -1186,7 +1214,8 @@
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Standard aluminum handbook value</t>
         </is>
@@ -1213,7 +1242,8 @@
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Standard aluminum handbook value</t>
         </is>
@@ -1240,7 +1270,8 @@
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Standard physical constant</t>
         </is>
@@ -1267,7 +1298,8 @@
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>CODATA</t>
         </is>
@@ -1281,7 +1313,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Mass-transfer inhibition constraint (g -&gt; 0 below this gap)</t>
+          <t>No longer a model constraint: the g -&gt; 0 wall below this gap was removed with the switch to the stratified Nu (no Ra_crit onset, so Sh -&gt; 1 is diffusion, not zero). Kept as the documented location of the old wall, which test_governing_equations asserts g is continuous across, and as the L_g sweep/optimizer lower bound.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1294,7 +1326,8 @@
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Sec. 2.2</t>
         </is>
@@ -1321,7 +1354,8 @@
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>CODATA</t>
         </is>
@@ -1348,7 +1382,8 @@
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Standard physical constant</t>
         </is>
@@ -1375,7 +1410,8 @@
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Numerical backstop, not a physical bound. The binding ceiling is computed per salt and per blend by physics.dilution_ceiling_c_w as the equilibrium c_w at this sheet's 'Dilution cap (maximum water activity)' (0.98), because the same water activity corresponds to a different water inventory for every salt. 400000 mol/m3 corresponds to a_w ~ 0.948 for LiCl, so it used to bind before the dilution cap existed and reconciled the three disagreeing caps; it is now only the value the inversions return when f_b &lt;= 0 makes the algebra undefined.</t>
         </is>
@@ -1402,7 +1438,8 @@
       </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Numerical backstop, not a physical bound. 100 mol/m3 is ~0.01-0.03 water molecules per salt formula unit, roughly 100x drier than any hydrate, i.e. no constraint at all. The binding desorption floor is computed per salt and per blend as n_hydrate * c_s (physics.hydrate_floor_c_w), with n_hydrate read from this workbook's Salts sheet 'hydrate_h2o_per_formula' column and blend-weighted over ZSR_SALTS; for baseline LiCl at S/L=4 that is 10444 mol/m3, ~100x this row. The alternative floor mode (SystemConfig(c_w_floor_mode='drh'), physics.drh_floor_c_w) stops at brine saturation instead, which is wetter still. This row is what those computed floors replaced, kept because the isotherm inversions still need a finite value to return on their degenerate branches.</t>
         </is>
@@ -1429,7 +1466,8 @@
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Methods (hydrogel cast at ~20% RH ambient)</t>
         </is>
@@ -1456,7 +1494,8 @@
       </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Device design assumption; distinct from Wilson et al. (2025) Table S3's L_c symbol, which denotes the insulation gap (tracked separately as this sheet's 'Insulation gap (L_ins)' row)</t>
         </is>
@@ -1481,7 +1520,7 @@
           <t>m^2*K/W</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>R_aluminum (L_c/k_Al = 5mm/167 W/m/K = 3.0e-5) + R_silicone (L_silicone/k_silicone = 1mm/0.2 W/m/K = 5.0e-3) = 5.03e-3, rounded to 0.005 m^2 K/W</t>
         </is>
@@ -1506,7 +1545,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Numerical guard, not a physical constant. Trapezoid closure error is &lt;=0.09% on a sound integration; an implicit-solver failure on the T_gel-clamp kink misses by 67-99%, so anything in between separates the two populations.</t>
         </is>
@@ -1531,7 +1570,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>IAPWS water critical point</t>
         </is>
@@ -1556,7 +1595,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>IAPWS water critical point</t>
         </is>
@@ -1581,7 +1620,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Numerical bracket, not physical; spans every salt's validated mass-fraction range</t>
         </is>
@@ -1606,7 +1645,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Numerical bracket, not physical; above every salt's saturation mass fraction</t>
         </is>
@@ -1631,7 +1670,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Ideal-gas beta = 1/T at ~300 K. Stored as the reference temperature, not as beta itself: 1/300 needs 17 significant digits and the workbook keeps 15, so storing beta directly loses the last bit.</t>
         </is>
@@ -1656,7 +1695,7 @@
           <t>W/(m*K)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Table S3</t>
         </is>
@@ -1681,7 +1720,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Numerical guard on the surface-temperature solve</t>
         </is>
@@ -1706,7 +1745,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Water critical point (373.946 C) less a small margin -- the ceiling of the Saul-Wagner p_sat correlation, which returns NaN at and above T_crit. Was 120 C, which no correlation required (the LiCl/CaCl2 isotherms carry their own separate 150 C guards) and which the thermal Newton solve's OUTPUT was clamped to: a design hotter than the ceiling silently reported the ceiling instead of erroring, and dc_w/dt kinks ~15x then goes flat exactly there, which is what made implicit ODE solvers diverge on the desorption RHS.</t>
         </is>
@@ -1731,7 +1770,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Lab synthesis geometry</t>
         </is>
@@ -1756,7 +1795,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Lab synthesis protocol</t>
         </is>
@@ -1781,7 +1820,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Lab synthesis protocol</t>
         </is>
@@ -1806,7 +1845,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Lab synthesis protocol</t>
         </is>
@@ -1831,7 +1870,7 @@
           <t>g/g</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Lab synthesis protocol</t>
         </is>
@@ -1856,7 +1895,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Lab synthesis protocol</t>
         </is>
@@ -1881,7 +1920,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Numerical tolerance on the blend simplex</t>
         </is>
@@ -1906,7 +1945,7 @@
           <t>count</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Linear interp on a smooth monotone curve, ~1e-6 relative</t>
         </is>
@@ -1931,7 +1970,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Cache granularity for the per-salt molality inversion</t>
         </is>
@@ -1956,7 +1995,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Keeps the tabulated window strictly inside the correlation's validity range</t>
         </is>
@@ -1981,7 +2020,7 @@
           <t>count</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Bilinear device-side lookup resolution</t>
         </is>
@@ -2006,7 +2045,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Spans the gel's operating range</t>
         </is>
@@ -2031,7 +2070,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Spans the gel's operating range</t>
         </is>
@@ -2056,7 +2095,7 @@
           <t>count</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>2.5 C spacing over 0-100 C</t>
         </is>
@@ -2081,7 +2120,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Note S2 (Atacama system)</t>
         </is>
@@ -2106,7 +2145,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Reconciles three caps that used to disagree: per-salt rh_max (0.97, NaCl 0.99), an rh&gt;=0.99 short-circuit in equilibrium_c_w_at_rh, and C_W_MAX=400000 mol/m3 (a_w~0.948, the binding one). Needed because a_w -&gt; 1 means infinite dilution: c_w diverges and the a_w -&gt; f_b inversion goes ill-conditioned as da_w/df_b -&gt; 0.</t>
         </is>
@@ -2120,7 +2159,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ISO 15099 aspect ratio A_g,i = H_cav / gap (Eq. 52), feeds Hollands Nu_2</t>
+          <t>ISO 15099 aspect ratio A_g,i = H_cav / gap, feeds Nu_2 (Eq. 52) of the stratified vapor-gap Nu</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2131,7 +2170,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Device is modelled per m^2 of absorber, hence 1 m. Nu_1 dominates Nu_2 for A_g,i &gt;~ 7 at this device's Ra, so the exact value does not bind.</t>
         </is>
@@ -2156,7 +2195,7 @@
           <t>W/m^2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Standard solar constant (Duffie &amp; Beckman)</t>
         </is>
@@ -2181,7 +2220,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Generic ground reflectance (Duffie &amp; Beckman)</t>
         </is>
@@ -2206,7 +2245,7 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Below ~3 deg solar elevation the division blows up on near-zero cos(zenith); clamp rather than emit a spurious POA spike.</t>
         </is>
@@ -2231,7 +2270,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Note S1 / COMSOL time step</t>
         </is>
@@ -2256,7 +2295,7 @@
           <t>hours</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) 12 h / 12 h duty cycle</t>
         </is>
@@ -2281,7 +2320,7 @@
           <t>W/m^2</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Numerical threshold on measured GHI noise</t>
         </is>
@@ -2306,7 +2345,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Numerical step, not physical. Small against the isotherm's temperature scale, large enough to stay off the a_w round-off floor.</t>
         </is>
@@ -2331,7 +2370,7 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Numerical, not physical, and no longer on any production path: instant equilibrium is now imposed as the equilibrium constraint itself (physics.equilibrium_t_gel_desorption_c / equilibrium_c_w_absorption), not by scaling g until Eq. 5's residual is negligible. This factor survives only as the legacy penalty route's setting, which tests/test_local_equilibrium.py pins the constraint against; 1e6 is the most converged reference of the values measured (1e5 sits 0.12% from it, 1e4 0.79%). It was briefly lowered to 1e5 to buy sweep time back when the penalty was still in use -- the constraint made that trade unnecessary, so it is restored.</t>
         </is>
@@ -2356,7 +2395,7 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Solver tolerance, not a physical constant</t>
         </is>
@@ -2381,7 +2420,7 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Solver tolerance, not a physical constant</t>
         </is>
@@ -2406,7 +2445,7 @@
           <t>kg/m^2/s</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Numerical bracket, not physical; ~2 orders above any reachable desorption flux</t>
         </is>
@@ -2431,7 +2470,7 @@
           <t>J/m^2/K</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2456,7 +2495,7 @@
           <t>m^2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Device is modelled per m^2 of contactor</t>
         </is>
@@ -2481,7 +2520,7 @@
           <t>dimensionless</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Non-selective contactor surface</t>
         </is>
@@ -2506,7 +2545,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2531,7 +2570,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2556,7 +2595,7 @@
           <t>W/K</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2581,7 +2620,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>1/8 inch aluminium plate (0.125 in x 0.0254 m/in)</t>
         </is>
@@ -2606,7 +2645,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Kept at 120 C rather than sharing the solar package's 373.9 C: that ceiling is the Saul-Wagner correlation's critical-point limit, and waste_heat uses Tetens (Magnus), which has no such ceiling. 120 C sits well above the 58 C waste-heat source, so the clamp is a divergence guard here, not a physical bound. The lower bound is shared (this sheet's 'Temperature clamp lower bound').</t>
         </is>
@@ -2631,7 +2670,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Standard atmosphere</t>
         </is>
@@ -2656,7 +2695,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Low-grade industrial waste-heat stream assumption</t>
         </is>
@@ -2681,7 +2720,7 @@
           <t>J/kg/K</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Liquid water at ~58 C</t>
         </is>
@@ -2706,7 +2745,7 @@
           <t>kg/s/m^2</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2731,7 +2770,7 @@
           <t>W/K</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2756,7 +2795,7 @@
           <t>kg/s/Pa/m^2</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2781,7 +2820,7 @@
           <t>kg/s/Pa/m^2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Sweep bound, not physical</t>
         </is>
@@ -2806,7 +2845,7 @@
           <t>kg/s/Pa/m^2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Sweep bound, not physical</t>
         </is>
@@ -2831,7 +2870,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Cycle control set point</t>
         </is>
@@ -2856,7 +2895,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>6 h cap on a half-cycle</t>
         </is>
@@ -2881,7 +2920,7 @@
           <t>1/(kg/m^2)</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2906,7 +2945,7 @@
           <t>1/(kg/s/m^2)</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Two-bed waste-heat device design assumption</t>
         </is>
@@ -2931,7 +2970,7 @@
           <t>degC</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Two-bed waste-heat siting assumption; distinct from the solar device's 25 degC</t>
         </is>
@@ -2956,7 +2995,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Two-bed waste-heat siting assumption; distinct from the solar device's 0.5</t>
         </is>
@@ -2981,7 +3020,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Numerical ramp, not physical</t>
         </is>
@@ -3006,7 +3045,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Profile resolution for the two-bed cycle</t>
         </is>
@@ -3031,7 +3070,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Diagnostic sampling resolution</t>
         </is>
@@ -3062,7 +3101,7 @@
       <c r="F99" t="n">
         <v>1.5</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>0 = passive. Wilson et al. (2025) Note S2 runs a 0.5 m/s fan array; the 1.5 m/s upper bound allows ~3x that.</t>
         </is>
@@ -3093,7 +3132,7 @@
       <c r="F100" t="n">
         <v>4</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Hours the seal/open boundaries move off GHI sunrise/sunset. +/-4 h covers sealing before dawn through holding shut well past dusk.</t>
         </is>
@@ -3118,7 +3157,7 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Numerical guard, not a physical constant. instant_equilibrium means the gel reaches equilibrium with the ambient RH, i.e. the residual driving force goes to zero -- the defining property, and checkable without a closed-form target for the equilibrium c_w (which cap binds, brine isotherm vs DVS uptake, varies with RH). Measured residual ratio is &lt;=1.5e-15 across RH 0.3-0.95 and the ZSR blends; a finite-g run sits at 1.1e-1, so this threshold has ~9 orders of headroom above a sound instant-equilibrium run and ~5 orders below a finite-g one.</t>
         </is>
@@ -3143,7 +3182,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>Standard atmosphere (sea level); lower it for high-altitude sites</t>
         </is>
@@ -3168,7 +3207,7 @@
           <t>m^2/s</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Wilson et al. (2025) Note S1 (Sh = Nu analogy)</t>
         </is>
@@ -3193,7 +3232,7 @@
           <t>m^2/s</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>Standard air property near 25 degC</t>
         </is>
@@ -3218,7 +3257,7 @@
           <t>kg/m^3</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Dry air, ~sea level, ~20 C</t>
         </is>
@@ -3243,7 +3282,7 @@
           <t>J/(kg*K)</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>Dry air, ~20 C</t>
         </is>
@@ -3274,7 +3313,7 @@
       <c r="F107" t="n">
         <v>0.8</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>Nu ~ Re^n Pr^(1/3), Re = uL/nu with nu ~ 1/rho; device Re ~ 3e4 is laminar (transition 5e5)</t>
         </is>
@@ -3294,14 +3333,14 @@
           <t>kg/m3</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>Dry-basis density of the PAM-LiCl composite: rho_composite(20% RH) 1250.2 / (1 + 1.2589), where 1.2589 g/g is the measured composite moisture content at the 20% RH fabrication equilibrium (Wilson Note S2 DVS). Recorded as a scalar because the DVS *isotherm* is no longer used as a sorption model -- water uptake now comes from the salt-in-water activity model alone (physics.water_activity_from_c_w). This is a mass/density calibration, not a sorption curve: it converts between dry composite mass and footprint volume for costing and gravimetric reporting. Value is bit-identical to what the derived expression returned.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G44"/>
+  <autoFilter ref="A1:H44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4987,7 +5026,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
